--- a/docentes/Valerio González Valeria - Estadisticos 20241.xlsx
+++ b/docentes/Valerio González Valeria - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -67,49 +67,58 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>CAMACHO</t>
   </si>
   <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
     <t>LEON</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>PAYRO</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>CUAHUA</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>URIEL ARTURO</t>
+  </si>
+  <si>
     <t>ALEXANDRO</t>
   </si>
   <si>
-    <t>CARMEN STEFANY</t>
-  </si>
-  <si>
     <t>BRYANA</t>
   </si>
   <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
     <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>LUIS ROBERTO</t>
   </si>
 </sst>
 </file>
@@ -575,16 +584,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -640,16 +652,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>42.5</v>
+        <v>45</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5.8</v>
       </c>
     </row>
   </sheetData>
@@ -659,7 +671,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -691,16 +703,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920142</v>
+        <v>24330051920093</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -714,16 +726,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920313</v>
+        <v>24330051920142</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -732,7 +744,7 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -743,10 +755,10 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -755,21 +767,21 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920147</v>
+        <v>24330051920149</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -778,21 +790,21 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920149</v>
+        <v>24330051920305</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -801,6 +813,29 @@
         <v>9</v>
       </c>
       <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>24330051920306</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Valerio González Valeria - Estadisticos 20241.xlsx
+++ b/docentes/Valerio González Valeria - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="61">
   <si>
     <t>Mat</t>
   </si>
@@ -67,6 +67,33 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>DURAN</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
@@ -85,6 +112,33 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>TLATEMOHUE</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>PAYRO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
@@ -101,6 +155,33 @@
   </si>
   <si>
     <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>VICTOR YAEL</t>
+  </si>
+  <si>
+    <t>EDWARD ALEXIS</t>
+  </si>
+  <si>
+    <t>CARLOS ANTONIO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>YARETH</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>RAMSES</t>
+  </si>
+  <si>
+    <t>DEREK</t>
+  </si>
+  <si>
+    <t>CARLOS ARGEL</t>
   </si>
   <si>
     <t>URIEL ARTURO</t>
@@ -671,7 +752,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -703,16 +784,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920093</v>
+        <v>24330051920092</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -721,21 +802,21 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920142</v>
+        <v>24330051920156</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -744,21 +825,21 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920403</v>
+        <v>24330051920143</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -767,21 +848,21 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920149</v>
+        <v>24330051920127</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -790,21 +871,21 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920305</v>
+        <v>24330051920098</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -813,29 +894,236 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920306</v>
+        <v>24330051920155</v>
       </c>
       <c r="B7" t="s">
         <v>21</v>
       </c>
       <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>24330051920147</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>24330051920113</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>24330051920315</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920093</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24330051920142</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>24330051920403</v>
+      </c>
+      <c r="B13" t="s">
         <v>27</v>
       </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7">
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>24330051920149</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>24330051920305</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>24330051920306</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Valerio González Valeria - Estadisticos 20241.xlsx
+++ b/docentes/Valerio González Valeria - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="74">
   <si>
     <t>Mat</t>
   </si>
@@ -67,36 +67,51 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DELGADO</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>DURAN</t>
+  </si>
+  <si>
     <t>APARICIO</t>
   </si>
   <si>
-    <t>DURAN</t>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>ROSAS</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>CAMACHO</t>
   </si>
   <si>
@@ -112,79 +127,103 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>RAMON</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>PAYRO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>MEZA</t>
   </si>
   <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
     <t>TLATEMOHUE</t>
   </si>
   <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>PAYRO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>CUAHUA</t>
   </si>
   <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>MARIA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ERWIN ISRAEL</t>
+  </si>
+  <si>
+    <t>EDWARD ALEXIS</t>
+  </si>
+  <si>
     <t>VICTOR YAEL</t>
   </si>
   <si>
-    <t>EDWARD ALEXIS</t>
+    <t>LEVI SANTIAGO</t>
+  </si>
+  <si>
+    <t>YARETH</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>RAMSES</t>
+  </si>
+  <si>
+    <t>MIRANDA ALIZEET</t>
+  </si>
+  <si>
+    <t>DEREK</t>
   </si>
   <si>
     <t>CARLOS ANTONIO</t>
   </si>
   <si>
+    <t>CARLOS ARGEL</t>
+  </si>
+  <si>
+    <t>URIEL ARTURO</t>
+  </si>
+  <si>
     <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>YARETH</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>DEREK</t>
-  </si>
-  <si>
-    <t>CARLOS ARGEL</t>
-  </si>
-  <si>
-    <t>URIEL ARTURO</t>
   </si>
   <si>
     <t>ALEXANDRO</t>
@@ -752,7 +791,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -784,16 +823,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920092</v>
+        <v>24330051920101</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -807,16 +846,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920156</v>
+        <v>24330051920104</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -830,16 +869,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920143</v>
+        <v>24330051920393</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -853,16 +892,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920127</v>
+        <v>24330051920156</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -876,16 +915,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920098</v>
+        <v>24330051920092</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -894,21 +933,21 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920155</v>
+        <v>24330051920392</v>
       </c>
       <c r="B7" t="s">
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -917,21 +956,21 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920147</v>
+        <v>24330051920098</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -940,21 +979,21 @@
         <v>9</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920113</v>
+        <v>24330051920155</v>
       </c>
       <c r="B9" t="s">
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -963,21 +1002,21 @@
         <v>9</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920315</v>
+        <v>24330051920147</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -986,21 +1025,21 @@
         <v>9</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920093</v>
+        <v>24330051920107</v>
       </c>
       <c r="B11" t="s">
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1014,16 +1053,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920142</v>
+        <v>24330051920113</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1032,21 +1071,21 @@
         <v>9</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920403</v>
+        <v>24330051920143</v>
       </c>
       <c r="B13" t="s">
         <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1055,21 +1094,21 @@
         <v>9</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920149</v>
+        <v>24330051920315</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1078,21 +1117,21 @@
         <v>9</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920305</v>
+        <v>24330051920093</v>
       </c>
       <c r="B15" t="s">
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1106,24 +1145,139 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920306</v>
+        <v>24330051920127</v>
       </c>
       <c r="B16" t="s">
         <v>30</v>
       </c>
       <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>24330051920142</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" t="s">
         <v>45</v>
       </c>
-      <c r="D16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16">
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>24330051920403</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>24330051920149</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>24330051920305</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>24330051920306</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Valerio González Valeria - Estadisticos 20241.xlsx
+++ b/docentes/Valerio González Valeria - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -67,9 +67,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
@@ -79,21 +76,12 @@
     <t>DURAN</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>APARICIO</t>
   </si>
   <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
     <t>PELLICO</t>
   </si>
   <si>
@@ -103,33 +91,6 @@
     <t>ROSAS</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
@@ -139,21 +100,12 @@
     <t>RAMON</t>
   </si>
   <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>PAYRO</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -163,27 +115,6 @@
     <t>MEZA</t>
   </si>
   <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TLATEMOHUE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CUAHUA</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
     <t>MARIA ESTEFANIA</t>
   </si>
   <si>
@@ -193,21 +124,12 @@
     <t>EDWARD ALEXIS</t>
   </si>
   <si>
+    <t>CARLOS ARGEL</t>
+  </si>
+  <si>
     <t>VICTOR YAEL</t>
   </si>
   <si>
-    <t>LEVI SANTIAGO</t>
-  </si>
-  <si>
-    <t>YARETH</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
     <t>MIRANDA ALIZEET</t>
   </si>
   <si>
@@ -215,30 +137,6 @@
   </si>
   <si>
     <t>CARLOS ANTONIO</t>
-  </si>
-  <si>
-    <t>CARLOS ARGEL</t>
-  </si>
-  <si>
-    <t>URIEL ARTURO</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>ALEXANDRO</t>
-  </si>
-  <si>
-    <t>BRYANA</t>
-  </si>
-  <si>
-    <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>LUIS ROBERTO</t>
   </si>
 </sst>
 </file>
@@ -772,16 +670,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>45</v>
+        <v>72.5</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
@@ -791,7 +689,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -823,16 +721,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920101</v>
+        <v>24330051920104</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -846,16 +744,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920104</v>
+        <v>24330051920393</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -869,16 +767,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920393</v>
+        <v>24330051920156</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -887,21 +785,21 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920156</v>
+        <v>24330051920315</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -921,10 +819,10 @@
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -938,16 +836,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920392</v>
+        <v>24330051920107</v>
       </c>
       <c r="B7" t="s">
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -961,16 +859,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920098</v>
+        <v>24330051920113</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -984,16 +882,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920155</v>
+        <v>24330051920143</v>
       </c>
       <c r="B9" t="s">
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1003,282 +901,6 @@
       </c>
       <c r="G9">
         <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>24330051920147</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920107</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920113</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24330051920143</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920315</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>24330051920093</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>24330051920127</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>24330051920142</v>
-      </c>
-      <c r="B17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>24330051920403</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>24330051920149</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>24330051920305</v>
-      </c>
-      <c r="B20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>24330051920306</v>
-      </c>
-      <c r="B21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" t="s">
-        <v>73</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Valerio González Valeria - Estadisticos 20241.xlsx
+++ b/docentes/Valerio González Valeria - Estadisticos 20241.xlsx
@@ -67,73 +67,73 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>DURAN</t>
+  </si>
+  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>DURAN</t>
-  </si>
-  <si>
     <t>VENTURA</t>
   </si>
   <si>
     <t>APARICIO</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>PELLICO</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>ROSAS</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
     <t>ZEPEDA</t>
   </si>
   <si>
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>MEZA</t>
   </si>
   <si>
+    <t>ERWIN ISRAEL</t>
+  </si>
+  <si>
+    <t>EDWARD ALEXIS</t>
+  </si>
+  <si>
     <t>MARIA ESTEFANIA</t>
   </si>
   <si>
-    <t>ERWIN ISRAEL</t>
-  </si>
-  <si>
-    <t>EDWARD ALEXIS</t>
-  </si>
-  <si>
     <t>CARLOS ARGEL</t>
   </si>
   <si>
     <t>VICTOR YAEL</t>
   </si>
   <si>
+    <t>DEREK</t>
+  </si>
+  <si>
     <t>MIRANDA ALIZEET</t>
-  </si>
-  <si>
-    <t>DEREK</t>
   </si>
   <si>
     <t>CARLOS ANTONIO</t>
@@ -721,7 +721,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920104</v>
+        <v>24330051920393</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -744,7 +744,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920393</v>
+        <v>24330051920156</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -762,12 +762,12 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920156</v>
+        <v>24330051920104</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
@@ -836,7 +836,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920107</v>
+        <v>24330051920113</v>
       </c>
       <c r="B7" t="s">
         <v>21</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920113</v>
+        <v>24330051920107</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
@@ -877,7 +877,7 @@
         <v>9</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -900,7 +900,7 @@
         <v>9</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
